--- a/CanaryBanana/site/Practica_TDH_CanaryBanana_soluciones.xlsx
+++ b/CanaryBanana/site/Practica_TDH_CanaryBanana_soluciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/CanaryBanana/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{3EE067C6-BAEB-44F1-A75B-F89285009983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A5233B0-FB3A-4774-A829-572CC4BEDCCE}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{3EE067C6-BAEB-44F1-A75B-F89285009983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87CFB437-A4F3-4A4F-A590-4505F68C9DCA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1785" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividad_TDH" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="75">
   <si>
     <t>Tipo</t>
   </si>
@@ -257,12 +257,6 @@
   </si>
   <si>
     <t>Fase 5 – Ecosistema digital avanzado</t>
-  </si>
-  <si>
-    <t>Resultado Correcto</t>
-  </si>
-  <si>
-    <t>Impacto Correcto</t>
   </si>
   <si>
     <t xml:space="preserve">INSTRUCCIONES:
@@ -329,7 +323,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -338,7 +332,55 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCE5FF"/>
+          <bgColor rgb="FFCCE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFFCC"/>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCE5FF"/>
+          <bgColor rgb="FFCCE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFFCC"/>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -374,10 +416,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -666,23 +704,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="4" width="45" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="110" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +735,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" t="s">
         <v>43</v>
@@ -705,7 +743,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
         <v>44</v>
@@ -713,7 +751,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
         <v>45</v>
@@ -721,7 +759,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>46</v>
@@ -729,7 +767,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>47</v>
@@ -737,7 +775,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>48</v>
@@ -745,7 +783,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" t="s">
         <v>49</v>
@@ -753,7 +791,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" t="s">
         <v>50</v>
@@ -761,7 +799,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
         <v>51</v>
@@ -769,7 +807,7 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" t="s">
         <v>52</v>
@@ -777,7 +815,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" t="s">
         <v>53</v>
@@ -785,7 +823,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" t="s">
         <v>54</v>
@@ -793,7 +831,7 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" t="s">
         <v>55</v>
@@ -801,7 +839,7 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" t="s">
         <v>56</v>
@@ -809,7 +847,7 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" t="s">
         <v>57</v>
@@ -817,7 +855,7 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" t="s">
         <v>58</v>
@@ -825,7 +863,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" t="s">
         <v>59</v>
@@ -833,7 +871,7 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" t="s">
         <v>60</v>
@@ -841,7 +879,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" t="s">
         <v>61</v>
@@ -849,7 +887,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" t="s">
         <v>62</v>
@@ -857,7 +895,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" t="s">
         <v>63</v>
@@ -865,7 +903,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" t="s">
         <v>64</v>
@@ -873,7 +911,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" t="s">
         <v>65</v>
@@ -881,7 +919,7 @@
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" t="s">
         <v>66</v>
@@ -889,7 +927,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" t="s">
         <v>67</v>
@@ -897,7 +935,7 @@
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" t="s">
         <v>68</v>
@@ -905,7 +943,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
         <v>69</v>
@@ -914,7 +952,7 @@
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
         <v>70</v>
@@ -923,7 +961,7 @@
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
         <v>71</v>
@@ -932,7 +970,7 @@
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
         <v>72</v>
@@ -941,7 +979,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
         <v>73</v>
@@ -955,13 +993,13 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:E33">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$A3="Agro"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$A3="NegociosInternacionales"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$A3="Fases"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -996,13 +1034,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="56.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1013,7 +1051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>24</v>
       </c>
@@ -1021,7 +1059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1032,7 +1070,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1043,7 +1081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1092,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>35</v>
       </c>
@@ -1062,7 +1100,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>39</v>
       </c>
@@ -1070,7 +1108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>33</v>
       </c>
@@ -1078,7 +1116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>20</v>
       </c>
@@ -1086,7 +1124,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>36</v>
       </c>
@@ -1094,7 +1132,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>14</v>
       </c>
@@ -1102,7 +1140,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>12</v>
       </c>
@@ -1110,7 +1148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>30</v>
       </c>
@@ -1118,7 +1156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>26</v>
       </c>
@@ -1126,42 +1164,42 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>9</v>
       </c>
@@ -1176,462 +1214,799 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="5"/>
+    <col min="3" max="3" width="24.21875" customWidth="1"/>
+    <col min="4" max="4" width="58.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.5546875" customWidth="1"/>
+    <col min="7" max="7" width="59.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5">
+        <f>IF(D1=G1,1,0)+IF(E1=H1,1,0)</f>
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f t="shared" ref="A2:A31" si="0">IF(D2=G2,1,0)+IF(E2=H2,1,0)</f>
+        <v>1</v>
+      </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H8" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="F17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E22" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="F22" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="F25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F30" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="F31" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" t="s">
-        <v>27</v>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
+        <f>SUM(A1:A31)/31*10</f>
+        <v>2.5806451612903225</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F1:H26 F27 H27 F28:H31">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$B1="Agro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$B1="NegociosInternacionales"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$B1="Fases"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26">
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>$B27="Agro"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>$B27="NegociosInternacionales"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
+      <formula>$B27="Fases"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>